--- a/fabrication/boards/bms-1_0/bom-bms-1_0_self-stuff.xlsx
+++ b/fabrication/boards/bms-1_0/bom-bms-1_0_self-stuff.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zbrozek-git\solarcar-batterypack\bms\bms_mainboard-1_0\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zbrozek-git\solarcar-batterypack\fabrication\boards\bms-1_0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B25305-F5CB-4FFC-B982-2910491CA21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7019656F-13CC-4DCF-9A1C-E05EB7DBB438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{E5A64653-0685-4BCC-9F43-0F10B860C9A2}"/>
+    <workbookView xWindow="8830" yWindow="2450" windowWidth="28200" windowHeight="18290" xr2:uid="{E5A64653-0685-4BCC-9F43-0F10B860C9A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-bms_mainboard" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="155">
   <si>
     <t>Designator</t>
   </si>
@@ -159,9 +159,6 @@
     <t>VICOR_HEATSINK_30183</t>
   </si>
   <si>
-    <t>HS2, HS3</t>
-  </si>
-  <si>
     <t>Heat Sink, 11ohm, Extruded, Clip, Longitudinal, Aluminum Alloy, Anodized</t>
   </si>
   <si>
@@ -283,6 +280,228 @@
   </si>
   <si>
     <t>4SIP</t>
+  </si>
+  <si>
+    <t>J14</t>
+  </si>
+  <si>
+    <t>SMA Connector Jack, Female Socket Panel Mount, Through Hole, Right Angle Solder, IP68 unmated</t>
+  </si>
+  <si>
+    <t>GCT (Gradconn)</t>
+  </si>
+  <si>
+    <t>RFPC-SMA14-FN-A</t>
+  </si>
+  <si>
+    <t>2072-RFPC-SMA14-FN-A-ND</t>
+  </si>
+  <si>
+    <t>C3173272</t>
+  </si>
+  <si>
+    <t>GCT_RFPC-SMA14-FN-A</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>J8</t>
+  </si>
+  <si>
+    <t>Conn RJ-45 F 8 POS 1.02mm Solder ST Thru-Hole 20 Terminal 1 Port Tray</t>
+  </si>
+  <si>
+    <t>Bel</t>
+  </si>
+  <si>
+    <t>V8BR-1AX1-GH</t>
+  </si>
+  <si>
+    <t>5923-V8BR-1AX1-GH-ND</t>
+  </si>
+  <si>
+    <t>C5346729</t>
+  </si>
+  <si>
+    <t>BELFUSE_V8BR-1AX1-GH</t>
+  </si>
+  <si>
+    <t>HS1, HS2, HS3</t>
+  </si>
+  <si>
+    <t>OHMITE_WA-T247-101E</t>
+  </si>
+  <si>
+    <t>J12</t>
+  </si>
+  <si>
+    <t>Conn Power PL 35 POS 4mm Solder RA Thru-Hole 35 Terminal 1 Port, BLACK</t>
+  </si>
+  <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
+    <t>1-776163-1</t>
+  </si>
+  <si>
+    <t>A106383-ND</t>
+  </si>
+  <si>
+    <t>C596198</t>
+  </si>
+  <si>
+    <t>TE_AMPSEAL_1-776163-1</t>
+  </si>
+  <si>
+    <t>J13</t>
+  </si>
+  <si>
+    <t>Conn Power PL 35 POS 4mm Solder RA Thru-Hole 35 Terminal 1 Port, BLUE</t>
+  </si>
+  <si>
+    <t>1-776163-5</t>
+  </si>
+  <si>
+    <t>1-776163-5-ND</t>
+  </si>
+  <si>
+    <t>C17378321</t>
+  </si>
+  <si>
+    <t>TE_AMPSEAL_1-776163-5</t>
+  </si>
+  <si>
+    <t>H4, H5, H6, H14, H15, H16</t>
+  </si>
+  <si>
+    <t>Standoff Round Swage F/F M3 X 0.5-THD Carbon Steel Electro-Tin ASTM B545</t>
+  </si>
+  <si>
+    <t>PennEngineering</t>
+  </si>
+  <si>
+    <t>SMTSO-M3-2ET</t>
+  </si>
+  <si>
+    <t>153-SMTSO-M3-2ET</t>
+  </si>
+  <si>
+    <t>C18212183</t>
+  </si>
+  <si>
+    <t>C60</t>
+  </si>
+  <si>
+    <t>Aluminum Electrolytic Capacitor, Polarized, Aluminum (wet), 220V, 20% +Tol, 20% -Tol, 220uF, Through Hole Mount</t>
+  </si>
+  <si>
+    <t>United Chemi-Con</t>
+  </si>
+  <si>
+    <t>EKXJ221ELL221MM25S</t>
+  </si>
+  <si>
+    <t>565-EKXJ221ELL221MM25S-ND</t>
+  </si>
+  <si>
+    <t>C1600234</t>
+  </si>
+  <si>
+    <t>CAP_1600X2700X750</t>
+  </si>
+  <si>
+    <t>H7, H8, H9, H10, H11, H12, H13</t>
+  </si>
+  <si>
+    <t>Pin Receptacle Connector 0.078" ~ 0.096" (1.98mm ~ 2.44mm) No Tail Solder</t>
+  </si>
+  <si>
+    <t>Preci-Dip</t>
+  </si>
+  <si>
+    <t>15115-91-0710</t>
+  </si>
+  <si>
+    <t>1212-15115-91-0710-ND</t>
+  </si>
+  <si>
+    <t>PRECI-DIP_15115-91-0710</t>
+  </si>
+  <si>
+    <t>R82, R84</t>
+  </si>
+  <si>
+    <t>RES TK FM 7.5 OHM 100W 1% TO247</t>
+  </si>
+  <si>
+    <t>TEH100M7R50FE</t>
+  </si>
+  <si>
+    <t>TEH100M7R50FE-ND</t>
+  </si>
+  <si>
+    <t>C2641795</t>
+  </si>
+  <si>
+    <t>TO-247-2_VERTICAL</t>
+  </si>
+  <si>
+    <t>R112</t>
+  </si>
+  <si>
+    <t>RES TK FM 470 OHM 100W 1% TO247</t>
+  </si>
+  <si>
+    <t>TEH100M470RJE</t>
+  </si>
+  <si>
+    <t>TEH100M470RJE-ND</t>
+  </si>
+  <si>
+    <t>C2642463</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>6-ch 2.5kV Isolator, 150M, 4/2, NB SOIC16, lead free</t>
+  </si>
+  <si>
+    <t>Skyworks Solutions</t>
+  </si>
+  <si>
+    <t>SI8662BB-B-IS1</t>
+  </si>
+  <si>
+    <t>SI8662BB-B-IS1-ND</t>
+  </si>
+  <si>
+    <t>C430287</t>
+  </si>
+  <si>
+    <t>16SOIC150</t>
+  </si>
+  <si>
+    <t>XF6</t>
+  </si>
+  <si>
+    <t>Fuse Holder 30 A 500V 1 Circuit Blade Through Hole</t>
+  </si>
+  <si>
+    <t>Keystone Electronics</t>
+  </si>
+  <si>
+    <t>3568</t>
+  </si>
+  <si>
+    <t>36-3568-ND</t>
+  </si>
+  <si>
+    <t>C3206956</t>
+  </si>
+  <si>
+    <t>FUSEHOLDER_KEYSTONE_3568</t>
   </si>
 </sst>
 </file>
@@ -666,525 +885,743 @@
     <col min="10" max="13" width="15.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
         <v>2</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>24</v>
+      <c r="I4" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>36</v>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2" t="s">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>2</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="E21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="G21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="G22" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
+        <v>1</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="G23" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
+        <v>1</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>

--- a/fabrication/boards/bms-1_0/bom-bms-1_0_self-stuff.xlsx
+++ b/fabrication/boards/bms-1_0/bom-bms-1_0_self-stuff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zbrozek-git\solarcar-batterypack\fabrication\boards\bms-1_0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7019656F-13CC-4DCF-9A1C-E05EB7DBB438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7B972B-FD50-408D-939E-B6E30B893FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8830" yWindow="2450" windowWidth="28200" windowHeight="18290" xr2:uid="{E5A64653-0685-4BCC-9F43-0F10B860C9A2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E5A64653-0685-4BCC-9F43-0F10B860C9A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-bms_mainboard" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="181">
   <si>
     <t>Designator</t>
   </si>
@@ -502,6 +502,84 @@
   </si>
   <si>
     <t>FUSEHOLDER_KEYSTONE_3568</t>
+  </si>
+  <si>
+    <t>R80, R83, R89</t>
+  </si>
+  <si>
+    <t>RES SMD 0.0005 OHM 1% 3W 2726</t>
+  </si>
+  <si>
+    <t>Vishay Dale</t>
+  </si>
+  <si>
+    <t>WSL2726L5000FEB</t>
+  </si>
+  <si>
+    <t>WSLQ-.0005CT-ND</t>
+  </si>
+  <si>
+    <t>C4132421</t>
+  </si>
+  <si>
+    <t>VISHAY_WSL2726</t>
+  </si>
+  <si>
+    <t>R90, R160</t>
+  </si>
+  <si>
+    <t>RES SMD 0.005 OHM 1% 3W 2726</t>
+  </si>
+  <si>
+    <t>WSL27265L000FEB</t>
+  </si>
+  <si>
+    <t>WSLQ-.005CT-ND</t>
+  </si>
+  <si>
+    <t>C1517421</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>DIODE ZENER 56V 200MW SOD</t>
+  </si>
+  <si>
+    <t>onsemi</t>
+  </si>
+  <si>
+    <t>MM3Z56VC</t>
+  </si>
+  <si>
+    <t>488-MM3Z56VCCT-ND</t>
+  </si>
+  <si>
+    <t>C891632</t>
+  </si>
+  <si>
+    <t>SOD323</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>CRYSTAL 32.768 KHZ 12.5 PF SMD</t>
+  </si>
+  <si>
+    <t>TXC CORPORATION</t>
+  </si>
+  <si>
+    <t>9HT10-32.768KEZF-T</t>
+  </si>
+  <si>
+    <t>887-1507-1-ND</t>
+  </si>
+  <si>
+    <t>C5932452</t>
+  </si>
+  <si>
+    <t>XTAL_TXC_9HT10</t>
   </si>
 </sst>
 </file>
@@ -878,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FA8C1D-083C-4E30-91D6-7A7C108953AA}">
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="8" width="15.81640625" customWidth="1"/>
@@ -1624,60 +1702,132 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
+      <c r="A25" s="1">
+        <v>3</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
+      <c r="A26" s="1">
+        <v>2</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
+      <c r="A27" s="1">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
+      <c r="A28" s="1">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
@@ -1914,8 +2064,8 @@
       <c r="H45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="2"/>
@@ -1942,7 +2092,7 @@
       <c r="H47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
-      <c r="L47" s="1"/>
+      <c r="L47" s="2"/>
       <c r="M47" s="1"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
@@ -1954,10 +2104,10 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
       <c r="L48" s="2"/>
-      <c r="M48" s="1"/>
+      <c r="M48" s="2"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="2"/>
@@ -1982,8 +2132,8 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
@@ -2026,8 +2176,8 @@
       <c r="H53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
@@ -2054,8 +2204,8 @@
       <c r="H55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="2"/>
@@ -2082,8 +2232,8 @@
       <c r="H57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="2"/>
@@ -2096,8 +2246,8 @@
       <c r="H58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="2"/>
@@ -2360,8 +2510,8 @@
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
     </row>
@@ -2556,8 +2706,8 @@
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
     </row>
@@ -2584,8 +2734,8 @@
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
     </row>
@@ -2626,8 +2776,8 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
-      <c r="J96" s="1"/>
-      <c r="K96" s="1"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
     </row>
@@ -2640,8 +2790,8 @@
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
     </row>
@@ -2682,8 +2832,8 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
-      <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
     </row>
@@ -2696,8 +2846,8 @@
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
     </row>
@@ -2934,8 +3084,8 @@
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
-      <c r="J118" s="1"/>
-      <c r="K118" s="1"/>
+      <c r="J118" s="2"/>
+      <c r="K118" s="2"/>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
     </row>
@@ -3118,8 +3268,8 @@
       <c r="H131" s="2"/>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
-      <c r="L131" s="2"/>
-      <c r="M131" s="2"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="1"/>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="2"/>
@@ -3132,8 +3282,8 @@
       <c r="H132" s="2"/>
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
-      <c r="L132" s="1"/>
-      <c r="M132" s="1"/>
+      <c r="L132" s="2"/>
+      <c r="M132" s="2"/>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="2"/>
@@ -3146,8 +3296,8 @@
       <c r="H133" s="2"/>
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
-      <c r="L133" s="2"/>
-      <c r="M133" s="2"/>
+      <c r="L133" s="1"/>
+      <c r="M133" s="1"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="2"/>
@@ -3160,8 +3310,8 @@
       <c r="H134" s="2"/>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
-      <c r="L134" s="1"/>
-      <c r="M134" s="1"/>
+      <c r="L134" s="2"/>
+      <c r="M134" s="2"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="2"/>
@@ -3188,8 +3338,8 @@
       <c r="H136" s="2"/>
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
-      <c r="L136" s="2"/>
-      <c r="M136" s="2"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="2"/>
@@ -3202,8 +3352,8 @@
       <c r="H137" s="2"/>
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
-      <c r="L137" s="1"/>
-      <c r="M137" s="1"/>
+      <c r="L137" s="2"/>
+      <c r="M137" s="2"/>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="2"/>
@@ -3244,8 +3394,8 @@
       <c r="H140" s="2"/>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
-      <c r="L140" s="2"/>
-      <c r="M140" s="2"/>
+      <c r="L140" s="1"/>
+      <c r="M140" s="1"/>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="2"/>
@@ -3258,8 +3408,8 @@
       <c r="H141" s="2"/>
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
-      <c r="L141" s="1"/>
-      <c r="M141" s="1"/>
+      <c r="L141" s="2"/>
+      <c r="M141" s="2"/>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" s="2"/>
@@ -3270,9 +3420,9 @@
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
-      <c r="J142" s="2"/>
-      <c r="K142" s="2"/>
-      <c r="L142" s="2"/>
+      <c r="J142" s="1"/>
+      <c r="K142" s="1"/>
+      <c r="L142" s="1"/>
       <c r="M142" s="2"/>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.35">
@@ -3284,9 +3434,9 @@
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
-      <c r="J143" s="1"/>
-      <c r="K143" s="1"/>
-      <c r="L143" s="1"/>
+      <c r="J143" s="2"/>
+      <c r="K143" s="2"/>
+      <c r="L143" s="2"/>
       <c r="M143" s="2"/>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.35">
@@ -3429,20 +3579,6 @@
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A154" s="2"/>
-      <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
-      <c r="E154" s="2"/>
-      <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-      <c r="H154" s="2"/>
-      <c r="J154" s="2"/>
-      <c r="K154" s="2"/>
-      <c r="L154" s="2"/>
-      <c r="M154" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="262" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
